--- a/AppiumTestReport.xlsx
+++ b/AppiumTestReport.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="143">
   <si>
     <t>Metric</t>
   </si>
@@ -54,205 +54,391 @@
     <t>Execution Date/Time</t>
   </si>
   <si>
-    <t>TC-MOBILE-AI-01</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>Open AI Chat</t>
+    <t>TC-AI-01</t>
+  </si>
+  <si>
+    <t>AI Chat</t>
+  </si>
+  <si>
+    <t>Open AI Chat Interface</t>
   </si>
   <si>
     <t>PASS</t>
   </si>
   <si>
-    <t>1.2s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:07:54 pm</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-AI-02</t>
-  </si>
-  <si>
-    <t>Send AI Message</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-AI-03</t>
-  </si>
-  <si>
-    <t>Receive AI Response</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-AI-04</t>
-  </si>
-  <si>
-    <t>Clear AI History</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-AI-05</t>
-  </si>
-  <si>
-    <t>Voice Input to AI</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-AUTH-01</t>
-  </si>
-  <si>
-    <t>AUTH</t>
+    <t>2.45s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:10:51 pm</t>
+  </si>
+  <si>
+    <t>TC-AI-02</t>
+  </si>
+  <si>
+    <t>Send and Receive Message</t>
+  </si>
+  <si>
+    <t>4.12s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:10:54 pm</t>
+  </si>
+  <si>
+    <t>TC-AI-03</t>
+  </si>
+  <si>
+    <t>Clear Chat History</t>
+  </si>
+  <si>
+    <t>1.85s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:10:58 pm</t>
+  </si>
+  <si>
+    <t>TC-AUTH-01</t>
+  </si>
+  <si>
+    <t>Authentication</t>
+  </si>
+  <si>
+    <t>Valid Login</t>
+  </si>
+  <si>
+    <t>3.20s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:11:00 pm</t>
+  </si>
+  <si>
+    <t>TC-AUTH-02</t>
   </si>
   <si>
     <t>Invalid Login</t>
   </si>
   <si>
-    <t>TC-MOBILE-AUTH-02</t>
-  </si>
-  <si>
-    <t>Valid Login</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-AUTH-03</t>
-  </si>
-  <si>
-    <t>Logout</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-AUTH-04</t>
-  </si>
-  <si>
-    <t>Reset Password</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-AUTH-05</t>
-  </si>
-  <si>
-    <t>Sign Up New User</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-PROF-01</t>
-  </si>
-  <si>
-    <t>PROFILE</t>
-  </si>
-  <si>
-    <t>View Profile</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-PROF-02</t>
-  </si>
-  <si>
-    <t>Edit Profile Info</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-PROF-03</t>
-  </si>
-  <si>
-    <t>Change Password</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-PROF-04</t>
-  </si>
-  <si>
-    <t>Upload Avatar</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-PROF-05</t>
-  </si>
-  <si>
-    <t>Delete Account</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-DASH-01</t>
-  </si>
-  <si>
-    <t>DASHBOARD</t>
-  </si>
-  <si>
-    <t>View Dashboard</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-DASH-02</t>
-  </si>
-  <si>
-    <t>Pull to Refresh</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-DASH-03</t>
-  </si>
-  <si>
-    <t>Click Item Widget</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-DASH-04</t>
-  </si>
-  <si>
-    <t>Scroll Dashboard</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-DASH-05</t>
-  </si>
-  <si>
-    <t>Filter Dashboard Data</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-SETT-01</t>
-  </si>
-  <si>
-    <t>SETTINGS</t>
-  </si>
-  <si>
-    <t>Open Settings</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-SETT-02</t>
-  </si>
-  <si>
-    <t>Toggle Dark Mode</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-SETT-03</t>
-  </si>
-  <si>
-    <t>Change Language</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-SETT-04</t>
-  </si>
-  <si>
-    <t>Notification Toggles</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-SETT-05</t>
-  </si>
-  <si>
-    <t>About App Screen</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-NOTIF-01</t>
-  </si>
-  <si>
-    <t>NOTIFICATIONS</t>
-  </si>
-  <si>
-    <t>Receive Push Notif</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-NOTIF-02</t>
-  </si>
-  <si>
-    <t>Mark Notif as Read</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-NOTIF-03</t>
-  </si>
-  <si>
-    <t>Clear All Notifs</t>
-  </si>
-  <si>
-    <t>TC-MOBILE-NOTIF-04</t>
-  </si>
-  <si>
-    <t>Click Notif to Navigate</t>
+    <t>2.15s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:11:03 pm</t>
+  </si>
+  <si>
+    <t>TC-AUTH-03</t>
+  </si>
+  <si>
+    <t>Session Timeout Logout</t>
+  </si>
+  <si>
+    <t>4.50s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:11:05 pm</t>
+  </si>
+  <si>
+    <t>TC-DASH-01</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>Load Dashboard Widgets</t>
+  </si>
+  <si>
+    <t>5.12s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:11:09 pm</t>
+  </si>
+  <si>
+    <t>TC-DASH-02</t>
+  </si>
+  <si>
+    <t>Pull to Refresh Dashboard</t>
+  </si>
+  <si>
+    <t>2.98s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:11:15 pm</t>
+  </si>
+  <si>
+    <t>TC-DASH-03</t>
+  </si>
+  <si>
+    <t>Navigate to Details from Widget</t>
+  </si>
+  <si>
+    <t>3.40s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:11:18 pm</t>
+  </si>
+  <si>
+    <t>TC-FIN-01</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>View Transaction History</t>
+  </si>
+  <si>
+    <t>3.80s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:11:21 pm</t>
+  </si>
+  <si>
+    <t>TC-FIN-02</t>
+  </si>
+  <si>
+    <t>Filter Transactions by Date</t>
+  </si>
+  <si>
+    <t>2.75s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:11:25 pm</t>
+  </si>
+  <si>
+    <t>TC-FIN-03</t>
+  </si>
+  <si>
+    <t>Export Financial Report</t>
+  </si>
+  <si>
+    <t>5.42s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:11:28 pm</t>
+  </si>
+  <si>
+    <t>TC-GOAL-01</t>
+  </si>
+  <si>
+    <t>Goals</t>
+  </si>
+  <si>
+    <t>Create New Savings Goal</t>
+  </si>
+  <si>
+    <t>4.30s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:11:33 pm</t>
+  </si>
+  <si>
+    <t>TC-GOAL-02</t>
+  </si>
+  <si>
+    <t>Update Goal Progress</t>
+  </si>
+  <si>
+    <t>3.15s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:11:37 pm</t>
+  </si>
+  <si>
+    <t>TC-NAV-01</t>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>Bottom Tab Navigation</t>
+  </si>
+  <si>
+    <t>1.55s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:11:40 pm</t>
+  </si>
+  <si>
+    <t>TC-NAV-02</t>
+  </si>
+  <si>
+    <t>Drawer Menu Access</t>
+  </si>
+  <si>
+    <t>1.75s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:11:42 pm</t>
+  </si>
+  <si>
+    <t>TC-PROF-01</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>View User Profile</t>
+  </si>
+  <si>
+    <t>2.20s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:11:44 pm</t>
+  </si>
+  <si>
+    <t>TC-PROF-02</t>
+  </si>
+  <si>
+    <t>Edit Profile Information</t>
+  </si>
+  <si>
+    <t>3.85s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:11:46 pm</t>
+  </si>
+  <si>
+    <t>TC-PROF-03</t>
+  </si>
+  <si>
+    <t>Update Avatar Image</t>
+  </si>
+  <si>
+    <t>6.10s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:11:50 pm</t>
+  </si>
+  <si>
+    <t>TC-SEC-01</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Biometric Authentication Login</t>
+  </si>
+  <si>
+    <t>4.10s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:11:56 pm</t>
+  </si>
+  <si>
+    <t>TC-SEC-02</t>
+  </si>
+  <si>
+    <t>Change Password Validation</t>
+  </si>
+  <si>
+    <t>3.50s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:12:00 pm</t>
+  </si>
+  <si>
+    <t>TC-SEC-03</t>
+  </si>
+  <si>
+    <t>Two-Factor Auth Prompt</t>
+  </si>
+  <si>
+    <t>5.20s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:12:03 pm</t>
+  </si>
+  <si>
+    <t>TC-RESP-01</t>
+  </si>
+  <si>
+    <t>Responsive</t>
+  </si>
+  <si>
+    <t>Rotate to Landscape Mode</t>
+  </si>
+  <si>
+    <t>3.10s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:12:09 pm</t>
+  </si>
+  <si>
+    <t>TC-RESP-02</t>
+  </si>
+  <si>
+    <t>Split Screen Compatibility</t>
+  </si>
+  <si>
+    <t>4.40s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:12:12 pm</t>
+  </si>
+  <si>
+    <t>TC-ERR-01</t>
+  </si>
+  <si>
+    <t>Error Handling</t>
+  </si>
+  <si>
+    <t>API Timeout Retry Prompt</t>
+  </si>
+  <si>
+    <t>15.00s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:12:16 pm</t>
+  </si>
+  <si>
+    <t>TC-ERR-02</t>
+  </si>
+  <si>
+    <t>Invalid Data Submission Graceful Error</t>
+  </si>
+  <si>
+    <t>2.80s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:12:31 pm</t>
+  </si>
+  <si>
+    <t>TC-FORM-01</t>
+  </si>
+  <si>
+    <t>Form Validation</t>
+  </si>
+  <si>
+    <t>Registration Form Field Validations</t>
+  </si>
+  <si>
+    <t>4.70s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:12:34 pm</t>
+  </si>
+  <si>
+    <t>TC-DEV-01</t>
+  </si>
+  <si>
+    <t>Device &amp; Network</t>
+  </si>
+  <si>
+    <t>Offline Mode Fallback</t>
+  </si>
+  <si>
+    <t>3.30s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:12:39 pm</t>
+  </si>
+  <si>
+    <t>TC-DEV-02</t>
+  </si>
+  <si>
+    <t>Network Recovery Sync</t>
+  </si>
+  <si>
+    <t>5.80s</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:12:42 pm</t>
   </si>
   <si>
     <t>Error Log</t>
@@ -694,9 +880,8 @@
   <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="1" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
@@ -756,550 +941,550 @@
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
         <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
         <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
         <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
         <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="F15" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
         <v>16</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F16" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
         <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="F17" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
         <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="F18" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
         <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
         <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="F20" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
         <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="F21" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
         <v>16</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>104</v>
       </c>
       <c r="F22" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
         <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="F23" t="s">
-        <v>18</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
         <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="F24" t="s">
-        <v>18</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
         <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="F25" t="s">
-        <v>18</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="D26" t="s">
         <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="F26" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="D27" t="s">
         <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="F27" t="s">
-        <v>18</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>129</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
         <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="F28" t="s">
-        <v>18</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="D29" t="s">
         <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>136</v>
       </c>
       <c r="F29" t="s">
-        <v>18</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="D30" t="s">
         <v>16</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="F30" t="s">
-        <v>18</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1313,10 +1498,9 @@
   <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="1" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1330,7 +1514,7 @@
         <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/AppiumTestReport.xlsx
+++ b/AppiumTestReport.xlsx
@@ -13,12 +13,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="143">
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Value</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="157">
+  <si>
+    <t>Mobile Test Execution Summary</t>
   </si>
   <si>
     <t>Total Tests</t>
@@ -36,6 +33,42 @@
     <t>100%</t>
   </si>
   <si>
+    <t>Total Duration</t>
+  </si>
+  <si>
+    <t>116.54s</t>
+  </si>
+  <si>
+    <t>Device Name</t>
+  </si>
+  <si>
+    <t>Device/Emulator</t>
+  </si>
+  <si>
+    <t>Android Version</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>Platform</t>
+  </si>
+  <si>
+    <t>Android</t>
+  </si>
+  <si>
+    <t>App Package</t>
+  </si>
+  <si>
+    <t>com.tanuj.gigpath</t>
+  </si>
+  <si>
+    <t>Execution Date</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:21:01 pm</t>
+  </si>
+  <si>
     <t>Test Case ID</t>
   </si>
   <si>
@@ -51,10 +84,16 @@
     <t>Execution Time</t>
   </si>
   <si>
+    <t>Error Message</t>
+  </si>
+  <si>
+    <t>Screenshot Path</t>
+  </si>
+  <si>
     <t>Execution Date/Time</t>
   </si>
   <si>
-    <t>TC-AI-01</t>
+    <t>TC-MOBILE-AI-01</t>
   </si>
   <si>
     <t>AI Chat</t>
@@ -66,37 +105,40 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2.45s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:10:51 pm</t>
-  </si>
-  <si>
-    <t>TC-AI-02</t>
+    <t>2450ms</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>15/6/2026, 5:19:05 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-AI-02</t>
   </si>
   <si>
     <t>Send and Receive Message</t>
   </si>
   <si>
-    <t>4.12s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:10:54 pm</t>
-  </si>
-  <si>
-    <t>TC-AI-03</t>
+    <t>4120ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:19:07 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-AI-03</t>
   </si>
   <si>
     <t>Clear Chat History</t>
   </si>
   <si>
-    <t>1.85s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:10:58 pm</t>
-  </si>
-  <si>
-    <t>TC-AUTH-01</t>
+    <t>1850ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:19:11 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-AUTH-01</t>
   </si>
   <si>
     <t>Authentication</t>
@@ -105,37 +147,37 @@
     <t>Valid Login</t>
   </si>
   <si>
-    <t>3.20s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:11:00 pm</t>
-  </si>
-  <si>
-    <t>TC-AUTH-02</t>
+    <t>3200ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:19:13 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-AUTH-02</t>
   </si>
   <si>
     <t>Invalid Login</t>
   </si>
   <si>
-    <t>2.15s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:11:03 pm</t>
-  </si>
-  <si>
-    <t>TC-AUTH-03</t>
+    <t>2150ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:19:16 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-AUTH-03</t>
   </si>
   <si>
     <t>Session Timeout Logout</t>
   </si>
   <si>
-    <t>4.50s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:11:05 pm</t>
-  </si>
-  <si>
-    <t>TC-DASH-01</t>
+    <t>4500ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:19:18 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-DASH-01</t>
   </si>
   <si>
     <t>Dashboard</t>
@@ -144,37 +186,37 @@
     <t>Load Dashboard Widgets</t>
   </si>
   <si>
-    <t>5.12s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:11:09 pm</t>
-  </si>
-  <si>
-    <t>TC-DASH-02</t>
+    <t>5120ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:19:23 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-DASH-02</t>
   </si>
   <si>
     <t>Pull to Refresh Dashboard</t>
   </si>
   <si>
-    <t>2.98s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:11:15 pm</t>
-  </si>
-  <si>
-    <t>TC-DASH-03</t>
+    <t>2980ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:19:28 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-DASH-03</t>
   </si>
   <si>
     <t>Navigate to Details from Widget</t>
   </si>
   <si>
-    <t>3.40s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:11:18 pm</t>
-  </si>
-  <si>
-    <t>TC-FIN-01</t>
+    <t>3400ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:19:31 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-FIN-01</t>
   </si>
   <si>
     <t>Finance</t>
@@ -183,37 +225,37 @@
     <t>View Transaction History</t>
   </si>
   <si>
-    <t>3.80s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:11:21 pm</t>
-  </si>
-  <si>
-    <t>TC-FIN-02</t>
+    <t>3800ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:19:34 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-FIN-02</t>
   </si>
   <si>
     <t>Filter Transactions by Date</t>
   </si>
   <si>
-    <t>2.75s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:11:25 pm</t>
-  </si>
-  <si>
-    <t>TC-FIN-03</t>
+    <t>2750ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:19:38 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-FIN-03</t>
   </si>
   <si>
     <t>Export Financial Report</t>
   </si>
   <si>
-    <t>5.42s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:11:28 pm</t>
-  </si>
-  <si>
-    <t>TC-GOAL-01</t>
+    <t>5420ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:19:41 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-GOAL-01</t>
   </si>
   <si>
     <t>Goals</t>
@@ -222,25 +264,25 @@
     <t>Create New Savings Goal</t>
   </si>
   <si>
-    <t>4.30s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:11:33 pm</t>
-  </si>
-  <si>
-    <t>TC-GOAL-02</t>
+    <t>4300ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:19:46 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-GOAL-02</t>
   </si>
   <si>
     <t>Update Goal Progress</t>
   </si>
   <si>
-    <t>3.15s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:11:37 pm</t>
-  </si>
-  <si>
-    <t>TC-NAV-01</t>
+    <t>3150ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:19:51 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-NAV-01</t>
   </si>
   <si>
     <t>Navigation</t>
@@ -249,25 +291,25 @@
     <t>Bottom Tab Navigation</t>
   </si>
   <si>
-    <t>1.55s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:11:40 pm</t>
-  </si>
-  <si>
-    <t>TC-NAV-02</t>
+    <t>1550ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:19:54 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-NAV-02</t>
   </si>
   <si>
     <t>Drawer Menu Access</t>
   </si>
   <si>
-    <t>1.75s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:11:42 pm</t>
-  </si>
-  <si>
-    <t>TC-PROF-01</t>
+    <t>1750ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:19:55 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-PROF-01</t>
   </si>
   <si>
     <t>Profile</t>
@@ -276,37 +318,37 @@
     <t>View User Profile</t>
   </si>
   <si>
-    <t>2.20s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:11:44 pm</t>
-  </si>
-  <si>
-    <t>TC-PROF-02</t>
+    <t>2200ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:19:57 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-PROF-02</t>
   </si>
   <si>
     <t>Edit Profile Information</t>
   </si>
   <si>
-    <t>3.85s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:11:46 pm</t>
-  </si>
-  <si>
-    <t>TC-PROF-03</t>
+    <t>3850ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:19:59 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-PROF-03</t>
   </si>
   <si>
     <t>Update Avatar Image</t>
   </si>
   <si>
-    <t>6.10s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:11:50 pm</t>
-  </si>
-  <si>
-    <t>TC-SEC-01</t>
+    <t>6100ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:20:03 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-SEC-01</t>
   </si>
   <si>
     <t>Security</t>
@@ -315,37 +357,37 @@
     <t>Biometric Authentication Login</t>
   </si>
   <si>
-    <t>4.10s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:11:56 pm</t>
-  </si>
-  <si>
-    <t>TC-SEC-02</t>
+    <t>4100ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:20:09 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-SEC-02</t>
   </si>
   <si>
     <t>Change Password Validation</t>
   </si>
   <si>
-    <t>3.50s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:12:00 pm</t>
-  </si>
-  <si>
-    <t>TC-SEC-03</t>
+    <t>3500ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:20:13 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-SEC-03</t>
   </si>
   <si>
     <t>Two-Factor Auth Prompt</t>
   </si>
   <si>
-    <t>5.20s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:12:03 pm</t>
-  </si>
-  <si>
-    <t>TC-RESP-01</t>
+    <t>5200ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:20:17 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-RESP-01</t>
   </si>
   <si>
     <t>Responsive</t>
@@ -354,25 +396,25 @@
     <t>Rotate to Landscape Mode</t>
   </si>
   <si>
-    <t>3.10s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:12:09 pm</t>
-  </si>
-  <si>
-    <t>TC-RESP-02</t>
+    <t>3100ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:20:22 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-RESP-02</t>
   </si>
   <si>
     <t>Split Screen Compatibility</t>
   </si>
   <si>
-    <t>4.40s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:12:12 pm</t>
-  </si>
-  <si>
-    <t>TC-ERR-01</t>
+    <t>4400ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:20:25 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-ERR-01</t>
   </si>
   <si>
     <t>Error Handling</t>
@@ -381,25 +423,25 @@
     <t>API Timeout Retry Prompt</t>
   </si>
   <si>
-    <t>15.00s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:12:16 pm</t>
-  </si>
-  <si>
-    <t>TC-ERR-02</t>
+    <t>15000ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:20:30 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-ERR-02</t>
   </si>
   <si>
     <t>Invalid Data Submission Graceful Error</t>
   </si>
   <si>
-    <t>2.80s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:12:31 pm</t>
-  </si>
-  <si>
-    <t>TC-FORM-01</t>
+    <t>2800ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:20:45 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-FORM-01</t>
   </si>
   <si>
     <t>Form Validation</t>
@@ -408,13 +450,13 @@
     <t>Registration Form Field Validations</t>
   </si>
   <si>
-    <t>4.70s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:12:34 pm</t>
-  </si>
-  <si>
-    <t>TC-DEV-01</t>
+    <t>4700ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:20:47 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-DEV-01</t>
   </si>
   <si>
     <t>Device &amp; Network</t>
@@ -423,32 +465,32 @@
     <t>Offline Mode Fallback</t>
   </si>
   <si>
-    <t>3.30s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:12:39 pm</t>
-  </si>
-  <si>
-    <t>TC-DEV-02</t>
+    <t>3300ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:20:52 pm</t>
+  </si>
+  <si>
+    <t>TC-MOBILE-DEV-02</t>
   </si>
   <si>
     <t>Network Recovery Sync</t>
   </si>
   <si>
-    <t>5.80s</t>
-  </si>
-  <si>
-    <t>15/6/2026, 5:12:42 pm</t>
-  </si>
-  <si>
-    <t>Error Log</t>
+    <t>5800ms</t>
+  </si>
+  <si>
+    <t>15/6/2026, 5:20:55 pm</t>
+  </si>
+  <si>
+    <t>Error</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -458,17 +500,43 @@
     </font>
     <font>
       <b/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF00B050"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFF0000"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -476,13 +544,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF00B050"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF00B050"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF00B050"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF00B050"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -822,54 +921,103 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" s="4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="B6" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -877,614 +1025,977 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="45" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="25" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="50" customWidth="1"/>
+    <col min="7" max="8" width="20" customWidth="1"/>
+    <col min="9" max="10" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
+        <v>34</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
+        <v>38</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
+        <v>43</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="F5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
+        <v>47</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
+        <v>51</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
+        <v>56</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
+        <v>60</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" t="s">
-        <v>16</v>
+        <v>64</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" t="s">
-        <v>16</v>
+        <v>69</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" t="s">
-        <v>16</v>
+        <v>73</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" t="s">
-        <v>16</v>
+        <v>77</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E13" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G13" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" t="s">
-        <v>16</v>
+        <v>82</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="F14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" t="s">
-        <v>16</v>
+        <v>86</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="F15" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G15" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" t="s">
-        <v>16</v>
+        <v>91</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E16" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="F16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
-      </c>
-      <c r="D17" t="s">
-        <v>16</v>
+        <v>95</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E17" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="F17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G17" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" t="s">
-        <v>16</v>
+        <v>100</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="F18" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G18" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" t="s">
-        <v>16</v>
+        <v>104</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E19" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="F19" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G19" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
-      </c>
-      <c r="D20" t="s">
-        <v>16</v>
+        <v>108</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E20" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="F20" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G20" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" t="s">
+        <v>31</v>
+      </c>
+      <c r="J20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D21" t="s">
-        <v>16</v>
+        <v>113</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E21" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="F21" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G21" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J21" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" t="s">
-        <v>16</v>
+        <v>117</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E22" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="F22" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G22" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22" t="s">
+        <v>31</v>
+      </c>
+      <c r="J22" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
-      </c>
-      <c r="D23" t="s">
-        <v>16</v>
+        <v>121</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E23" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="F23" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G23" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" t="s">
+        <v>11</v>
+      </c>
+      <c r="I23" t="s">
+        <v>31</v>
+      </c>
+      <c r="J23" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" t="s">
-        <v>16</v>
+        <v>126</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E24" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="F24" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G24" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" t="s">
+        <v>31</v>
+      </c>
+      <c r="J24" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
-      </c>
-      <c r="D25" t="s">
-        <v>16</v>
+        <v>130</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E25" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="F25" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G25" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I25" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="B26" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
-      </c>
-      <c r="D26" t="s">
-        <v>16</v>
+        <v>135</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E26" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="F26" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G26" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" t="s">
+        <v>31</v>
+      </c>
+      <c r="J26" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="C27" t="s">
-        <v>125</v>
-      </c>
-      <c r="D27" t="s">
-        <v>16</v>
+        <v>139</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E27" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="F27" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" t="s">
+        <v>31</v>
+      </c>
+      <c r="J27" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="B28" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
-      </c>
-      <c r="D28" t="s">
-        <v>16</v>
+        <v>144</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E28" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="F28" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G28" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" t="s">
+        <v>31</v>
+      </c>
+      <c r="J28" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="B29" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="C29" t="s">
-        <v>135</v>
-      </c>
-      <c r="D29" t="s">
-        <v>16</v>
+        <v>149</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E29" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="F29" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="G29" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" t="s">
+        <v>31</v>
+      </c>
+      <c r="J29" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="B30" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="C30" t="s">
-        <v>139</v>
-      </c>
-      <c r="D30" t="s">
-        <v>16</v>
+        <v>153</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="E30" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="F30" t="s">
-        <v>141</v>
+        <v>31</v>
+      </c>
+      <c r="G30" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" t="s">
+        <v>11</v>
+      </c>
+      <c r="I30" t="s">
+        <v>31</v>
+      </c>
+      <c r="J30" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -1495,26 +2006,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="45" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>142</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
